--- a/branches/dependabot/github_actions/dev/actions-63cfa41bca/all-profiles.xlsx
+++ b/branches/dependabot/github_actions/dev/actions-63cfa41bca/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc2</t>
+    <t>2027.0.0-ballot.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-13T09:23:50+00:00</t>
+    <t>2026-09-14T09:50:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
